--- a/data.xlsx
+++ b/data.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sajee\Desktop\mail-merge-using-python-and-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D9BE865-FB4A-4A70-94EF-815A392C5A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D1499E-C7C0-4189-B3DA-0074EC981E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2196" yWindow="2196" windowWidth="17280" windowHeight="8964" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>name</t>
   </si>
@@ -34,19 +35,16 @@
     <t>kopimenan@gmail.com</t>
   </si>
   <si>
-    <t>priyankan</t>
-  </si>
-  <si>
     <t>attachment</t>
   </si>
   <si>
     <t>kopi</t>
   </si>
   <si>
-    <t>pri</t>
-  </si>
-  <si>
-    <t>pripriyankan3@gmail.com</t>
+    <t>abineyan</t>
+  </si>
+  <si>
+    <t>abineyan034@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -378,7 +376,8 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -389,7 +388,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -400,24 +399,50 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
+      <c r="B3" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A5678C8-0DDD-4874-ACFC-46ADA0E16B4B}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{EEDC0E53-96A3-47BD-AEBF-6F03DB153454}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
